--- a/kanji_data.xlsx
+++ b/kanji_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1JeTC735xH0AYKEZHrlVrGX49WCae_-Md\00-WORK\100-Projects\#作成アプリ\漢字プリント生成\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBB3CBD-5F9B-4598-9E42-BB7AC6822588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F22A1E0-835B-495D-88E7-6FC04BBE6B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="0" windowWidth="32330" windowHeight="20880" xr2:uid="{323655D3-8FFB-E245-9D31-8E6D6D4A8258}"/>
+    <workbookView xWindow="9030" yWindow="0" windowWidth="26010" windowHeight="20880" xr2:uid="{323655D3-8FFB-E245-9D31-8E6D6D4A8258}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8492" uniqueCount="5299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8495" uniqueCount="5300">
   <si>
     <t>教材名</t>
     <rPh sb="0" eb="3">
@@ -36749,6 +36749,10 @@
     <rPh sb="11" eb="12">
       <t>オコナ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>じょ/せい/よう</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -47749,6 +47753,9 @@
       <c r="F363" t="s">
         <v>1489</v>
       </c>
+      <c r="G363" t="s">
+        <v>5299</v>
+      </c>
       <c r="H363" s="1" t="s">
         <v>1008</v>
       </c>
@@ -48344,7 +48351,7 @@
         <v>4091</v>
       </c>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A385" t="s">
         <v>7</v>
       </c>
@@ -48370,7 +48377,7 @@
         <v>4092</v>
       </c>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A386" t="s">
         <v>7</v>
       </c>
@@ -48399,7 +48406,7 @@
         <v>4093</v>
       </c>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A387" t="s">
         <v>7</v>
       </c>
@@ -48425,7 +48432,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A388" t="s">
         <v>7</v>
       </c>
@@ -48451,7 +48458,7 @@
         <v>4095</v>
       </c>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A389" t="s">
         <v>7</v>
       </c>
@@ -48480,7 +48487,7 @@
         <v>4096</v>
       </c>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A390" t="s">
         <v>7</v>
       </c>
@@ -48503,7 +48510,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A391" t="s">
         <v>7</v>
       </c>
@@ -48532,7 +48539,7 @@
         <v>4097</v>
       </c>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A392" t="s">
         <v>7</v>
       </c>
@@ -48561,7 +48568,7 @@
         <v>4098</v>
       </c>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A393" t="s">
         <v>7</v>
       </c>
@@ -48587,7 +48594,7 @@
         <v>4099</v>
       </c>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A394" t="s">
         <v>7</v>
       </c>
@@ -48616,7 +48623,7 @@
         <v>4100</v>
       </c>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A395" t="s">
         <v>7</v>
       </c>
@@ -48645,7 +48652,7 @@
         <v>4104</v>
       </c>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A396" t="s">
         <v>7</v>
       </c>
@@ -48674,7 +48681,7 @@
         <v>4101</v>
       </c>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A397" t="s">
         <v>7</v>
       </c>
@@ -48703,7 +48710,7 @@
         <v>4102</v>
       </c>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A398" t="s">
         <v>7</v>
       </c>
@@ -48729,7 +48736,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A399" t="s">
         <v>7</v>
       </c>
@@ -48755,7 +48762,7 @@
         <v>4105</v>
       </c>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.6">
       <c r="A400" t="s">
         <v>7</v>
       </c>
@@ -48782,6 +48789,12 @@
       </c>
       <c r="J400" t="s">
         <v>4109</v>
+      </c>
+      <c r="K400" t="s">
+        <v>1138</v>
+      </c>
+      <c r="L400" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.6">
